--- a/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De San Cristóbal.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De San Cristóbal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2850F011-28F0-4D41-B62E-979F15D86E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E3F03C-8650-3C4B-AD60-0834967DD0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6619AB33-F015-4EB6-8AA5-1F33AD98FD42}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{6619AB33-F015-4EB6-8AA5-1F33AD98FD42}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,11 +172,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -268,10 +278,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,8 +299,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -604,9 +619,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D83AAFD-5D3D-4861-BDFA-BC7BD31B09D9}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="162.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="168" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -678,35 +693,35 @@
         <v>21</v>
       </c>
       <c r="H2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="187.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="196" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -725,35 +740,35 @@
         <v>21</v>
       </c>
       <c r="H3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="225" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="252" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -772,35 +787,35 @@
         <v>21</v>
       </c>
       <c r="H4" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L4" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N4" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P4" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="225" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="252" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -819,35 +834,35 @@
         <v>21</v>
       </c>
       <c r="H5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="112.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="112" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -864,35 +879,35 @@
         <v>21</v>
       </c>
       <c r="H6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="98" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -907,35 +922,35 @@
         <v>21</v>
       </c>
       <c r="H7" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="N7" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="P7" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="200" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="256" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
@@ -949,42 +964,42 @@
       <c r="E8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" ht="200" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="238" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
@@ -1005,35 +1020,35 @@
         <v>21</v>
       </c>
       <c r="H9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" ht="225" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="252" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
@@ -1054,35 +1069,35 @@
         <v>21</v>
       </c>
       <c r="H10" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L10" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>25</v>
       </c>
       <c r="P10" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" ht="225" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="252" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1131,7 +1146,7 @@
       </c>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" ht="200" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="238" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1193,7 @@
       </c>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" ht="187.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="224" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
@@ -1223,7 +1238,7 @@
       </c>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17" ht="150" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="168" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -1267,6 +1282,9 @@
       <c r="Q14" s="5"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{B9457C91-E7D0-1147-9068-E1EE40223B3B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>